--- a/Burse/Licenta/Etapa_5.xlsx
+++ b/Burse/Licenta/Etapa_5.xlsx
@@ -173,7 +173,7 @@
     <t>RCC (2)</t>
   </si>
   <si>
-    <t>Etapa :0 ,Studentul Emplid: 3036 Nume: , Bursa: BP2, Program: RCC (2), cu media 9.58 are aceeași medie ca studentul Emplid: 3037, Nume: , Bursa: NU, Program: RCC (2), dar nu a primit bursă.</t>
+    <t>Etapa :0 ,Studentul Emplid: 3036 Nume: , Bursa: BP1, Program: RCC (2), cu media 9.58 are aceeași medie ca studentul Emplid: 3037, Nume: , Bursa: NU, Program: RCC (2), dar nu a primit bursă.</t>
   </si>
   <si>
     <t>SC (1)</t>
@@ -556,7 +556,7 @@
       </c>
       <c r="E24" s="10"/>
       <c r="F24" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" s="10"/>
       <c r="H24" s="10">
@@ -732,11 +732,11 @@
         <f>(1671770.95/1200)*B30</f>
       </c>
       <c r="D30" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="10"/>
       <c r="H30" s="10">
@@ -971,11 +971,11 @@
         <f>(1671770.95/1200)*B38</f>
       </c>
       <c r="D38" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="10"/>
       <c r="F38" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" s="10"/>
       <c r="H38" s="10">
@@ -1608,11 +1608,11 @@
         <f>(1671770.95/1200)*B59</f>
       </c>
       <c r="D59" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" s="18"/>
       <c r="F59" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G59" s="18"/>
       <c r="H59" s="18">
